--- a/providers/invesco/2026-06-23/invesco_etf_export.xlsx
+++ b/providers/invesco/2026-06-23/invesco_etf_export.xlsx
@@ -7424,10 +7424,10 @@
         <v>0.12</v>
       </c>
       <c r="G181">
-        <v>26931022679.65</v>
+        <v>26516852515.65</v>
       </c>
       <c r="H181">
-        <v>403.7793</v>
+        <v>397.8661</v>
       </c>
       <c r="I181"/>
     </row>
@@ -7461,10 +7461,10 @@
         <v>0.12</v>
       </c>
       <c r="G182">
-        <v>1061288731.17</v>
+        <v>1045631394.72</v>
       </c>
       <c r="H182">
-        <v>94.4395</v>
+        <v>93.0463</v>
       </c>
       <c r="I182"/>
     </row>
@@ -7498,10 +7498,10 @@
         <v>0.12</v>
       </c>
       <c r="G183">
-        <v>339371827.79</v>
+        <v>334386338.39</v>
       </c>
       <c r="H183">
-        <v>91.1097</v>
+        <v>89.7712</v>
       </c>
       <c r="I183"/>
     </row>
@@ -7535,10 +7535,10 @@
         <v>0.12</v>
       </c>
       <c r="G184">
-        <v>965279.46</v>
+        <v>951143.11</v>
       </c>
       <c r="H184">
-        <v>4.1969</v>
+        <v>4.1354</v>
       </c>
       <c r="I184"/>
     </row>
@@ -7572,10 +7572,10 @@
         <v>0.19</v>
       </c>
       <c r="G185">
-        <v>28804276.78</v>
+        <v>28076060.43</v>
       </c>
       <c r="H185">
-        <v>120.5765</v>
+        <v>117.5281</v>
       </c>
       <c r="I185"/>
     </row>
@@ -7609,10 +7609,10 @@
         <v>0.19</v>
       </c>
       <c r="G186">
-        <v>80231370.58</v>
+        <v>85475025.62</v>
       </c>
       <c r="H186">
-        <v>160.3877</v>
+        <v>156.7676</v>
       </c>
       <c r="I186"/>
     </row>
@@ -7646,10 +7646,10 @@
         <v>0.19</v>
       </c>
       <c r="G187">
-        <v>988240997.22</v>
+        <v>926275624.41</v>
       </c>
       <c r="H187">
-        <v>63.1931</v>
+        <v>59.2307</v>
       </c>
       <c r="I187"/>
     </row>
